--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488209_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488209_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7422</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1394</v>
+        <v>1.2373</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3971</v>
@@ -610,10 +610,10 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1306</v>
+        <v>-0.0326</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2736</v>
+        <v>-0.1756</v>
       </c>
       <c r="U2" t="n">
         <v>0.143</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0733</v>
+        <v>0.1731</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4502</v>
+        <v>0.5895</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3769</v>
+        <v>-0.4163</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0675</v>
+        <v>1.0736</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3702</v>
+        <v>0.0766</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4377</v>
+        <v>0.9969</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3992</v>
+        <v>1.7693</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3992</v>
+        <v>0.4422</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.3271</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4667</v>
+        <v>-0.6957</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.029</v>
+        <v>-0.3656</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4377</v>
+        <v>-0.3301</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0672</v>
+        <v>-0.5929</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9774</v>
+        <v>-0.2534</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0898</v>
+        <v>-0.3395</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0271</v>
+        <v>-0.4247</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2957</v>
+        <v>0.543</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2686</v>
+        <v>-0.9677</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0736</v>
+        <v>-0.7278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0766</v>
+        <v>-0.7985</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9969</v>
+        <v>0.0706</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7693</v>
+        <v>1.8014</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4422</v>
+        <v>1.1165</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3271</v>
+        <v>0.6849</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6957</v>
+        <v>-2.5292</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3656</v>
+        <v>-1.915</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3301</v>
+        <v>-0.6143</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7389</v>
+        <v>-0.9389</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5471</v>
+        <v>-0.332</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1918</v>
+        <v>-0.6069</v>
       </c>
       <c r="V4" t="n">
-        <v>0.063</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.063</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5232</v>
+        <v>-0.8086</v>
       </c>
       <c r="E5" t="n">
-        <v>0.543</v>
+        <v>-0.3332</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0662</v>
+        <v>-0.4754</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7278</v>
+        <v>-0.0675</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7985</v>
+        <v>0.3702</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0706</v>
+        <v>-0.4377</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8014</v>
+        <v>0.3992</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1165</v>
+        <v>0.3992</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6849</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5292</v>
+        <v>-0.4667</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.915</v>
+        <v>-0.029</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6143</v>
+        <v>-0.4377</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0374</v>
+        <v>0.1853</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.332</v>
+        <v>0.194</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7053</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1586</v>
+        <v>-1.4227</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4501</v>
+        <v>-0.9604</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7085</v>
+        <v>-0.4623</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4979</v>
@@ -922,13 +922,13 @@
         <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0382</v>
+        <v>-1.3023</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.766</v>
+        <v>-0.2764</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2721</v>
+        <v>-1.0259</v>
       </c>
       <c r="V6" t="n">
         <v>0.3774</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4643</v>
+        <v>-2.1705</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0695</v>
+        <v>1.3633</v>
       </c>
       <c r="F7" t="n">
         <v>-3.5338</v>
@@ -1000,10 +1000,10 @@
         <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9264</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8207</v>
+        <v>-0.5269</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1057</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0596</v>
+        <v>-3.1659</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2841</v>
+        <v>-0.4943</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7755</v>
+        <v>-2.6716</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2003</v>
+        <v>-1.4088</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.3722</v>
+        <v>0.5281</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1719</v>
+        <v>-1.9368</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2081</v>
+        <v>1.8423</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1478</v>
+        <v>1.7902</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9397</v>
+        <v>0.0522</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9922</v>
+        <v>-3.2511</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2244</v>
+        <v>-1.2621</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7678</v>
+        <v>-1.989</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.8307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2226</v>
+        <v>-0.4837</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5138</v>
+        <v>-0.347</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0624</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4837</v>
+        <v>-3.1821</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.886</v>
+        <v>-2.382</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5978</v>
+        <v>-0.8001</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4088</v>
+        <v>-2.2003</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5281</v>
+        <v>-3.3722</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9368</v>
+        <v>1.1719</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8423</v>
+        <v>-0.2081</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7902</v>
+        <v>-2.1478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0522</v>
+        <v>1.9397</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2511</v>
+        <v>-1.9922</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2621</v>
+        <v>-1.2244</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.989</v>
+        <v>-0.7678</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1485</v>
+        <v>-0.859</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8754</v>
+        <v>-0.3205</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2731</v>
+        <v>-0.5385</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.0624</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6788</v>
+        <v>-3.9491</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4149</v>
+        <v>-3.5128</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2639</v>
+        <v>-0.4362</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6967</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3213</v>
+        <v>-0.5916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>-0.2111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2082</v>
+        <v>-0.3805</v>
       </c>
       <c r="V10" t="n">
         <v>1.6363</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1963</v>
+        <v>-4.442</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2805</v>
+        <v>-1.3784</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9159</v>
+        <v>-3.0636</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1796</v>
@@ -1312,13 +1312,13 @@
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7849</v>
+        <v>-1.0306</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.332</v>
+        <v>-0.4299</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4529</v>
+        <v>-0.6006</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0847</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.360900000000001</v>
+        <v>-8.5305</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0998</v>
+        <v>-4.5895</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2611</v>
+        <v>-3.9411</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2386</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5103</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3209</v>
+        <v>-0.1688</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8312</v>
+        <v>-0.5111</v>
       </c>
       <c r="V12" t="n">
         <v>0.3144</v>
@@ -1426,10 +1426,10 @@
         <v>-27.0828</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.9176</v>
+        <v>-9.9175</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.1653</v>
+        <v>-17.1652</v>
       </c>
       <c r="G13" t="n">
         <v>-20.7563</v>
@@ -1441,7 +1441,7 @@
         <v>-8.947199999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5039</v>
+        <v>3.503899999999998</v>
       </c>
       <c r="K13" t="n">
         <v>2.1612</v>
@@ -1468,13 +1468,13 @@
         <v>12.0437</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.3057</v>
+        <v>-7.3058</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9842</v>
+        <v>-2.9843</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3213</v>
+        <v>-4.321400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.832</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2501</v>
+        <v>7.3693</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2465</v>
+        <v>6.2672</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0036</v>
+        <v>1.102</v>
       </c>
       <c r="G14" t="n">
         <v>3.7624</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2642</v>
+        <v>1.3834</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1737</v>
+        <v>1.1944</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0905</v>
+        <v>0.189</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8854</v>
+        <v>7.1809</v>
       </c>
       <c r="E15" t="n">
         <v>5.7188</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1666</v>
+        <v>1.462</v>
       </c>
       <c r="G15" t="n">
         <v>4.1951</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8374</v>
+        <v>1.1329</v>
       </c>
       <c r="T15" t="n">
         <v>0.7586000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0788</v>
+        <v>0.3743</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7251</v>
+        <v>5.5583</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4864</v>
+        <v>5.1719</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2387</v>
+        <v>0.3864</v>
       </c>
       <c r="G16" t="n">
         <v>4.7213</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4785</v>
+        <v>0.3547</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8754</v>
+        <v>-0.1899</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3969</v>
+        <v>0.5446</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6294</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2686</v>
+        <v>3.6407</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7881</v>
+        <v>3.215</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4805</v>
+        <v>0.4257</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6393</v>
+        <v>2.7584</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2121</v>
+        <v>2.1117</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5728</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4591</v>
+        <v>2.8251</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5882</v>
+        <v>2.7007</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8709</v>
+        <v>0.1244</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8198</v>
+        <v>-0.0667</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6239</v>
+        <v>-0.589</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4437</v>
+        <v>0.5223</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3154</v>
+        <v>0.3264</v>
       </c>
       <c r="T17" t="n">
-        <v>0.868</v>
+        <v>0.3899</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4474</v>
+        <v>-0.0634</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0313</v>
+        <v>3.508</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8025</v>
+        <v>2.5773</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2288</v>
+        <v>0.9307</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7584</v>
+        <v>3.5787</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1117</v>
+        <v>2.2348</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.3439</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8251</v>
+        <v>4.4974</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7007</v>
+        <v>2.5162</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1244</v>
+        <v>1.9812</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0667</v>
+        <v>-0.9187</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.589</v>
+        <v>-0.2814</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5223</v>
+        <v>-0.6373</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.717</v>
+        <v>0.484</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9774</v>
+        <v>0.2478</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2604</v>
+        <v>0.2363</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9456</v>
+        <v>3.2362</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8918</v>
+        <v>1.4943</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0538</v>
+        <v>1.7418</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5787</v>
+        <v>1.6393</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2348</v>
+        <v>2.2121</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3439</v>
+        <v>-0.5728</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4974</v>
+        <v>2.4591</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5162</v>
+        <v>1.5882</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9812</v>
+        <v>0.8709</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9187</v>
+        <v>-0.8198</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2814</v>
+        <v>0.6239</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6373</v>
+        <v>-1.4437</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0784</v>
+        <v>1.283</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4377</v>
+        <v>0.5742</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3594</v>
+        <v>0.7088</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0011</v>
+        <v>0.3139</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.315</v>
+        <v>0.3139</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.833</v>
+        <v>1.7116</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5002</v>
+        <v>0.2064</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3328</v>
+        <v>1.5052</v>
       </c>
       <c r="G20" t="n">
         <v>1.8382</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1806</v>
+        <v>1.0592</v>
       </c>
       <c r="T20" t="n">
-        <v>1.302</v>
+        <v>1.0082</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1214</v>
+        <v>0.051</v>
       </c>
       <c r="V20" t="n">
         <v>-0.63</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOSA LLANO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1412</v>
+        <v>0.4288</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4497</v>
+        <v>-0.5362</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3085</v>
+        <v>0.965</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9774</v>
+        <v>1.5838</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5565</v>
+        <v>1.4885</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4209</v>
+        <v>0.0953</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2346</v>
+        <v>2.4417</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4811</v>
+        <v>1.6016</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7157</v>
+        <v>0.8401</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.212</v>
+        <v>-0.858</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1131</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1366</v>
+        <v>-0.7448</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>-1.297</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2478</v>
+        <v>0.1421</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1416</v>
+        <v>-0.1986</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1062</v>
+        <v>0.3407</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>J. SOSA LLANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0619</v>
+        <v>-0.2264</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.83</v>
+        <v>0.156</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7681</v>
+        <v>-0.3824</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5838</v>
+        <v>-0.9774</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4885</v>
+        <v>-0.5565</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0953</v>
+        <v>-0.4209</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4417</v>
+        <v>0.2346</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6016</v>
+        <v>-0.4811</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8401</v>
+        <v>0.7157</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.858</v>
+        <v>-1.212</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1131</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7448</v>
+        <v>-1.1366</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3487</v>
+        <v>0.8801</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4924</v>
+        <v>0.8478</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1437</v>
+        <v>0.0323</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5789</v>
+        <v>-2.6287</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6891</v>
+        <v>-3.5912</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1103</v>
+        <v>0.9625</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9705</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0525</v>
+        <v>-0.1023</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3305</v>
+        <v>0.1828</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3566</v>
+        <v>-2.6957</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1996</v>
+        <v>-3.5141</v>
       </c>
       <c r="F24" t="n">
-        <v>0.843</v>
+        <v>0.8184</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3729</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2987</v>
+        <v>0.3622</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7113</v>
+        <v>-0.0258</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4126</v>
+        <v>0.388</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5733</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.0829</v>
+        <v>27.08300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>17.1653</v>
+        <v>17.1654</v>
       </c>
       <c r="F25" t="n">
-        <v>9.9177</v>
+        <v>9.917299999999999</v>
       </c>
       <c r="G25" t="n">
         <v>20.7564</v>
@@ -2395,7 +2395,7 @@
         <v>-1.3428</v>
       </c>
       <c r="P25" t="n">
-        <v>1.852800000000001</v>
+        <v>1.8528</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.0437</v>
@@ -2404,13 +2404,13 @@
         <v>13.8965</v>
       </c>
       <c r="S25" t="n">
-        <v>7.305599999999999</v>
+        <v>7.305699999999999</v>
       </c>
       <c r="T25" t="n">
         <v>4.3215</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9842</v>
+        <v>2.9844</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8321</v>
